--- a/Result/profitability/9944.xlsx
+++ b/Result/profitability/9944.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.24</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.05124999999999999</v>
+        <v>0.10375</v>
       </c>
       <c r="N2" t="n">
-        <v>25.26125</v>
+        <v>26.64</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>-0.2</v>
       </c>
       <c r="M3" t="n">
-        <v>0.02875</v>
+        <v>0.115</v>
       </c>
       <c r="N3" t="n">
-        <v>25.2675</v>
+        <v>27.2175</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.39</v>
       </c>
       <c r="M4" t="n">
-        <v>0.11375</v>
+        <v>0.10875</v>
       </c>
       <c r="N4" t="n">
-        <v>25.79375</v>
+        <v>25.65375</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.43</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1125</v>
+        <v>0.18375</v>
       </c>
       <c r="N5" t="n">
-        <v>23.8775</v>
+        <v>23.9825</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>0.35</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1775</v>
+        <v>0.27625</v>
       </c>
       <c r="N6" t="n">
-        <v>22.735</v>
+        <v>24.23</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.44</v>
       </c>
       <c r="M7" t="n">
-        <v>0.28125</v>
+        <v>0.3375</v>
       </c>
       <c r="N7" t="n">
-        <v>23.54</v>
+        <v>24.33375</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.54</v>
       </c>
       <c r="M8" t="n">
-        <v>0.355</v>
+        <v>0.32375</v>
       </c>
       <c r="N8" t="n">
-        <v>23.65625</v>
+        <v>23.32625</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1403,7 +1403,7 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>9944</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>687</v>
+      </c>
+      <c r="D75" t="n">
+        <v>467</v>
+      </c>
+      <c r="E75" t="n">
+        <v>220</v>
+      </c>
+      <c r="F75" t="n">
+        <v>31.99</v>
+      </c>
+      <c r="G75" t="n">
+        <v>60</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>8.78%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>24</v>
+      </c>
+      <c r="J75" t="n">
+        <v>85</v>
+      </c>
+      <c r="K75" t="n">
+        <v>42</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.03124999999999999</v>
+      </c>
+      <c r="N75" t="n">
+        <v>26.7375</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.3846153846153846</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-2.640000000000004</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.07623447877562817</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-3.352941176470588</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>0.8399999999999999</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.02696629213483148</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
